--- a/exports/40/route_40_2026-05-01_to_2026-05-15_analytics.xlsx
+++ b/exports/40/route_40_2026-05-01_to_2026-05-15_analytics.xlsx
@@ -97602,7 +97602,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B7"/>
+  <dimension ref="A1:B9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -97680,10 +97680,32 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>num_raw_rows</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>437366</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>artifact_type</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>local_excel_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
           <t>summary_excel_output</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>/home/mireles/horseless/telemetry_to_bi/exports/40/route_40_2026-05-01_to_2026-05-15_analytics.xlsx</t>
         </is>
